--- a/order_generation/PO_excel_export/test-2.xlsx
+++ b/order_generation/PO_excel_export/test-2.xlsx
@@ -350,7 +350,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1362075" cy="1266825"/>
+    <ext cx="1562100" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -358,6 +358,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1362075" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -761,7 +786,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>XX印刷厂</t>
+          <t>义乌市一柠饰品有限公司</t>
         </is>
       </c>
       <c r="C3" s="16" t="n"/>
@@ -787,7 +812,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>13605889085</t>
+          <t>0574-27889688</t>
         </is>
       </c>
       <c r="C4" s="16" t="n"/>
@@ -800,7 +825,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2025年11月04日</t>
+          <t>2025年12月30日</t>
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
@@ -811,11 +836,7 @@
           <t>联系人：</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>郑小姐</t>
-        </is>
-      </c>
+      <c r="B5" s="16" t="inlineStr"/>
       <c r="C5" s="16" t="n"/>
       <c r="D5" s="16" t="n"/>
       <c r="E5" s="16" t="n"/>
@@ -826,7 +847,7 @@
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>孙诚昱</t>
+          <t>郑遥杰</t>
         </is>
       </c>
       <c r="H5" s="16" t="n"/>
@@ -872,40 +893,51 @@
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>17-A1KN-KJGW-1</t>
+          <t>EEHB-NBB-1C</t>
         </is>
       </c>
       <c r="B7" s="29" t="n"/>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>黑人卷发梳双面印刷哑膜过UV，500g白卡</t>
+          <t>浅咖色</t>
         </is>
       </c>
       <c r="D7" s="29" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="F7" s="29">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="29" t="inlineStr">
-        <is>
-          <t>发泰丰</t>
-        </is>
-      </c>
+      <c r="G7" s="29" t="inlineStr"/>
       <c r="H7" s="20" t="n"/>
     </row>
-    <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="29" t="n"/>
+    <row r="8" ht="100" customFormat="1" customHeight="1" s="2">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-1B</t>
+        </is>
+      </c>
       <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F8" s="29">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="29" t="inlineStr"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
@@ -956,7 +988,7 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>宁波鄞州福庆南路2520号 宁波泰丰机械有限公司，郑小姐，13605889085</t>
+          <t>瑾秀地址：浙江宁波市余姚市陆埠镇五马工业区创利西路 15 号 多多 15258337865</t>
         </is>
       </c>
       <c r="C12" s="25" t="n"/>
@@ -972,7 +1004,11 @@
           <t>付款方式:</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr"/>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>开专票，价格已含税运</t>
+        </is>
+      </c>
       <c r="C13" s="25" t="n"/>
       <c r="D13" s="25" t="n"/>
       <c r="E13" s="25" t="n"/>
@@ -996,7 +1032,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年11月11日</t>
+          <t>15天</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>
@@ -1065,7 +1101,10 @@
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="4">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>放2%余量</t>
+          <t>义乌市一柠饰品有限公司
+税号:91330782MA2HQR5A51
+对公账号:201000320634668
+开户行:浙江义乌农村商业银行股份有限公司鹏城支行</t>
         </is>
       </c>
       <c r="B19" s="25" t="n"/>
@@ -1077,7 +1116,11 @@
       <c r="H19" s="25" t="n"/>
     </row>
     <row r="20" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A20" s="25" t="inlineStr"/>
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>开专票，价格已含税运</t>
+        </is>
+      </c>
       <c r="B20" s="25" t="n"/>
       <c r="C20" s="25" t="n"/>
       <c r="D20" s="25" t="n"/>
@@ -1087,7 +1130,11 @@
       <c r="H20" s="25" t="n"/>
     </row>
     <row r="21" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A21" s="25" t="inlineStr"/>
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>瑾秀地址：浙江宁波市余姚市陆埠镇五马工业区创利西路 15 号 多多 15258337865</t>
+        </is>
+      </c>
       <c r="B21" s="25" t="n"/>
       <c r="C21" s="25" t="n"/>
       <c r="D21" s="25" t="n"/>
@@ -1342,7 +1389,7 @@
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>XX印刷厂</t>
+          <t>义乌市一柠饰品有限公司</t>
         </is>
       </c>
       <c r="F69" s="9" t="n"/>

--- a/order_generation/PO_excel_export/test-2.xlsx
+++ b/order_generation/PO_excel_export/test-2.xlsx
@@ -350,7 +350,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1562100" cy="1266825"/>
+    <ext cx="1019175" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -358,31 +358,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1362075" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -786,7 +761,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>义乌市一柠饰品有限公司</t>
+          <t>和鑫制刷厂</t>
         </is>
       </c>
       <c r="C3" s="16" t="n"/>
@@ -812,7 +787,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>0574-27889688</t>
+          <t>15105029337</t>
         </is>
       </c>
       <c r="C4" s="16" t="n"/>
@@ -825,7 +800,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2025年12月30日</t>
+          <t>2026年02月02日</t>
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
@@ -836,7 +811,11 @@
           <t>联系人：</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr"/>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>朱春景</t>
+        </is>
+      </c>
       <c r="C5" s="16" t="n"/>
       <c r="D5" s="16" t="n"/>
       <c r="E5" s="16" t="n"/>
@@ -847,7 +826,7 @@
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>郑遥杰</t>
+          <t>孙诚昱</t>
         </is>
       </c>
       <c r="H5" s="16" t="n"/>
@@ -893,51 +872,40 @@
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>EEHB-NBB-1C</t>
+          <t>US-RB01-01</t>
         </is>
       </c>
       <c r="B7" s="29" t="n"/>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>浅咖色</t>
+          <t>禾木清洁刷清漆，3.1*7.3*1.1 厘米48孔。尼龙刷毛出峰2.5cm，加粗0.7mm，刷子表面和刷面清洁不要有碎屑附着,背后要加印logo Norsewood激光logo,散货</t>
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>0.45</v>
+        <v>10.8</v>
       </c>
       <c r="F7" s="29">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="29" t="inlineStr"/>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>如描述中要求</t>
+        </is>
+      </c>
       <c r="H7" s="20" t="n"/>
     </row>
-    <row r="8" ht="100" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>EEHB-NBB-1B</t>
-        </is>
-      </c>
+    <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
+      <c r="A8" s="29" t="n"/>
       <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="inlineStr">
-        <is>
-          <t>黑色</t>
-        </is>
-      </c>
-      <c r="D8" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F8" s="29">
-        <f>D8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="29" t="inlineStr"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
@@ -988,7 +956,7 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>瑾秀地址：浙江宁波市余姚市陆埠镇五马工业区创利西路 15 号 多多 15258337865</t>
+          <t>做好发到 小张 18668289261 浙江省 宁波市 海曙区 高桥镇高强路8号吉秀制刷</t>
         </is>
       </c>
       <c r="C12" s="25" t="n"/>
@@ -1004,11 +972,7 @@
           <t>付款方式:</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>开专票，价格已含税运</t>
-        </is>
-      </c>
+      <c r="B13" s="25" t="inlineStr"/>
       <c r="C13" s="25" t="n"/>
       <c r="D13" s="25" t="n"/>
       <c r="E13" s="25" t="n"/>
@@ -1099,14 +1063,7 @@
       <c r="H18" s="25" t="n"/>
     </row>
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>义乌市一柠饰品有限公司
-税号:91330782MA2HQR5A51
-对公账号:201000320634668
-开户行:浙江义乌农村商业银行股份有限公司鹏城支行</t>
-        </is>
-      </c>
+      <c r="A19" s="25" t="inlineStr"/>
       <c r="B19" s="25" t="n"/>
       <c r="C19" s="25" t="n"/>
       <c r="D19" s="25" t="n"/>
@@ -1116,11 +1073,7 @@
       <c r="H19" s="25" t="n"/>
     </row>
     <row r="20" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>开专票，价格已含税运</t>
-        </is>
-      </c>
+      <c r="A20" s="25" t="inlineStr"/>
       <c r="B20" s="25" t="n"/>
       <c r="C20" s="25" t="n"/>
       <c r="D20" s="25" t="n"/>
@@ -1130,11 +1083,7 @@
       <c r="H20" s="25" t="n"/>
     </row>
     <row r="21" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>瑾秀地址：浙江宁波市余姚市陆埠镇五马工业区创利西路 15 号 多多 15258337865</t>
-        </is>
-      </c>
+      <c r="A21" s="25" t="inlineStr"/>
       <c r="B21" s="25" t="n"/>
       <c r="C21" s="25" t="n"/>
       <c r="D21" s="25" t="n"/>
@@ -1389,7 +1338,7 @@
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>义乌市一柠饰品有限公司</t>
+          <t>和鑫制刷厂</t>
         </is>
       </c>
       <c r="F69" s="9" t="n"/>

--- a/order_generation/PO_excel_export/test-2.xlsx
+++ b/order_generation/PO_excel_export/test-2.xlsx
@@ -419,7 +419,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1019175" cy="1266825"/>
+    <ext cx="1104900" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>和鑫制刷厂</t>
+          <t>菲迪印刷</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -809,11 +809,7 @@
           <t>电话：</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>15105029337</t>
-        </is>
-      </c>
+      <c r="B4" s="9" t="inlineStr"/>
       <c r="C4" s="9" t="n"/>
       <c r="D4" s="10" t="n"/>
       <c r="E4" s="9" t="n"/>
@@ -824,7 +820,7 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>2026年02月02日</t>
+          <t>2026年02月03日</t>
         </is>
       </c>
       <c r="H4" s="9" t="n"/>
@@ -838,7 +834,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>朱春景</t>
+          <t>XX印刷厂</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -899,30 +895,26 @@
     <row r="7" ht="100" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>US-RB01-01</t>
+          <t>EC221-1-1</t>
         </is>
       </c>
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>禾木清洁刷清漆，3.1*7.3*1.1 厘米48孔。尼龙刷毛出峰2.5cm，加粗0.7mm，刷子表面和刷面清洁不要有碎屑附着,背后要加印logo Norsewood激光logo,散货</t>
+          <t>鱼骨梳包装，350g白卡双面印刷，FSC 绿色</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2222</v>
+        <v>1200</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>10.8</v>
+        <v>0.45</v>
       </c>
       <c r="F7" s="17">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>如描述中要求</t>
-        </is>
-      </c>
+      <c r="G7" s="16" t="inlineStr"/>
       <c r="H7" s="15" t="n"/>
       <c r="I7" s="34" t="n"/>
     </row>
@@ -988,7 +980,7 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>做好发到 小张 18668289261 浙江省 宁波市 海曙区 高桥镇高强路8号吉秀制刷</t>
+          <t>瑾秀 收货信息是瑾秀：浙江宁波市余姚市陆埠镇五马工业区创利西路 15 号 18067420259 多多</t>
         </is>
       </c>
       <c r="C12" s="21" t="n"/>
@@ -1005,7 +997,11 @@
           <t>付款方式:</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>出货后45天凭增值税发票付款</t>
+        </is>
+      </c>
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="22" t="n"/>
       <c r="E13" s="21" t="n"/>
@@ -1030,7 +1026,7 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>15天</t>
+          <t>7天</t>
         </is>
       </c>
       <c r="C14" s="21" t="n"/>
@@ -1102,7 +1098,11 @@
       <c r="I18" s="34" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1">
-      <c r="A19" s="21" t="inlineStr"/>
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>放2%余量</t>
+        </is>
+      </c>
       <c r="B19" s="21" t="n"/>
       <c r="C19" s="21" t="n"/>
       <c r="D19" s="22" t="n"/>
@@ -1659,14 +1659,14 @@
       <c r="A69" s="34" t="n"/>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>宁波品秀美容科技有限公司</t>
+          <t>宁波集秀美容科技有限公司</t>
         </is>
       </c>
       <c r="C69" s="29" t="n"/>
       <c r="D69" s="30" t="n"/>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>和鑫制刷厂</t>
+          <t>XX印刷厂</t>
         </is>
       </c>
       <c r="F69" s="31" t="n"/>
